--- a/feedback_forms/027_team_leadership_assessment_form--feedback_forms.xlsx
+++ b/feedback_forms/027_team_leadership_assessment_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,20 +525,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Team Leadership Form</t>
+          <t>Team Leadership Style</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -554,14 +554,14 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,20 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Team Adaptability</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Team Leadership Skills</t>
+          <t>Team Performance</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Team Dynamics</t>
+          <t>Time Management</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Areas for Improvement</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Team Leadership Skills</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,20 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Team Leadership Assessment</t>
+          <t>Teamwork</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Team Performance</t>
+          <t>Team Collaboration</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,358 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Team Performance Indicators</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>team_leadership_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Team Leadership Skills</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>team_leadership_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Time Management</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>team_leadership_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>team_leadership_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>team_leadership_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Team Leadership Skills</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>time_leadership_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>team_leadership_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>team_leadership_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>team_leadership_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Team Leadership Skills</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>team_leadership_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>team_leadership_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>team_leadership_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Team Leadership Skills</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>team_leadership_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>team_leadership_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Team Leadership Skills</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>team_leadership_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Team Performance</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1131,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>team_leadership</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Team Leadership</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1148,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>team_collaboration</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Team Collaboration</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1165,189 +820,189 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>team_leadership_4_choices</t>
+          <t>team_leadership_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>leadership</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>team_leadership_4_choices</t>
+          <t>team_leadership_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>team_leadership_4_choices</t>
+          <t>team_leadership_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>problem_solving</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Problem Solving</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>team_leadership_4_choices</t>
+          <t>team_leadership_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>team_collaboration</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Team Collaboration</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>team_leadership_4_choices</t>
+          <t>team_leadership_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>team_communication</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adaptability</t>
+          <t>Team Communication</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>team_leadership_5_choices</t>
+          <t>team_leadership_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>team_leadership_5_choices</t>
+          <t>team_leadership_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>team_leadership_5_choices</t>
+          <t>team_leadership_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Adaptability</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>team_leadership_5_choices</t>
+          <t>team_leadership_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>team_leadership_5_choices</t>
+          <t>team_leadership_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>team_leadership_6_choices</t>
+          <t>team_leadership_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,262 +1019,262 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>team_leadership_6_choices</t>
+          <t>team_leadership_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Trust</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>team_leadership_7_choices</t>
+          <t>team_leadership_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>team_leadership_7_choices</t>
+          <t>team_leadership_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>team_leadership_8_choices</t>
+          <t>team_leadership_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>team_leadership</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Team Leadership</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>team_leadership_8_choices</t>
+          <t>team_leadership_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>team_leadership_8_choices</t>
+          <t>team_leadership_5_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>team_collaboration</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Team Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>team_leadership_8_choices</t>
+          <t>team_leadership_6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>team_communication</t>
+          <t>team_performance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Team Communication</t>
+          <t>Team Performance</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>team_leadership_9_choices</t>
+          <t>team_leadership_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>team_performance</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Team Performance</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>team_leadership_9_choices</t>
+          <t>team_leadership_7_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>team_leadership_10_choices</t>
+          <t>team_leadership_7_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>team_leadership_10_choices</t>
+          <t>team_leadership_7_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>team_leadership_11_choices</t>
+          <t>team_leadership_7_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>leadership</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>team_leadership_11_choices</t>
+          <t>team_leadership_7_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>team_leadership_11_choices</t>
+          <t>team_leadership_8_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>problem_solving</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Problem Solving</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>team_leadership_11_choices</t>
+          <t>team_leadership_8_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Trust</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>team_leadership_11_choices</t>
+          <t>team_leadership_8_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,41 +1291,41 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>team_leadership_12_choices</t>
+          <t>team_leadership_8_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>team_leadership_12_choices</t>
+          <t>team_leadership_8_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>team_leadership_13_choices</t>
+          <t>team_leadership_9_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,782 +1342,119 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>team_leadership_13_choices</t>
+          <t>team_leadership_9_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>team_collaboration</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>Team Collaboration</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>team_leadership_13_choices</t>
+          <t>team_leadership_9_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>team_communication</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Adaptability</t>
+          <t>Team Communication</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>team_leadership_13_choices</t>
+          <t>team_leadership_10_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>team_leadership_13_choices</t>
+          <t>team_leadership_10_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>Trust</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>team_leadership_14_choices</t>
+          <t>team_leadership_10_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>teamwork</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>team_leadership_14_choices</t>
+          <t>team_leadership_10_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>team_leadership_15_choices</t>
+          <t>team_leadership_10_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>leadership</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>team_leadership_15_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>team_leadership_15_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>problem_solving</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Problem Solving</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>team_leadership_15_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
           <t>Time Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>team_leadership_15_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>time_leadership_16_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>teamwork</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>time_leadership_16_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>team_leadership_17_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>team_leadership</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>team_leadership_17_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>team_leadership_18_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>teamwork</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>team_leadership_18_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Trust</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>team_leadership_18_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>team_leadership_18_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>team_leadership_18_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Time Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>team_leadership_19_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>leadership</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>team_leadership_19_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>team_leadership_19_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>problem_solving</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Problem Solving</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>team_leadership_19_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Time Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>team_leadership_19_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>team_leadership_20_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>teamwork</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>team_leadership_20_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Trust</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>team_leadership_20_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>team_leadership_20_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>team_leadership_20_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Time Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>team_leadership_21_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>teamwork</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>team_leadership_21_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>team_leadership_22_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>leadership</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>team_leadership_22_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>team_leadership_22_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>problem_solving</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Problem Solving</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>team_leadership_22_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Time Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>team_leadership_22_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>team_leadership_23_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>teamwork</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Teamwork</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>team_leadership_23_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>team_leadership_24_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>leadership</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Leadership</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>team_leadership_24_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>team_leadership_24_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>problem_solving</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Problem Solving</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>team_leadership_24_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>time_management</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Time Management</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>team_leadership_24_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>team_leadership_25_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>team_performance</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Team Performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>team_leadership_25_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
